--- a/_data/PLCTags_FG05.xlsx
+++ b/_data/PLCTags_FG05.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R36a25049ed3d4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rf3f6cce24e924088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="Rc1926b7280d54efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rb4712ca9bf5a4b3a"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="72">
   <x:si>
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
@@ -195,6 +195,30 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">%Q506.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG05_Y_CapsSourceStopper_HomePos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q505.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG05_M_Bunker</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q507.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sortiertopf ein</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG05_M_Conveyor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q507.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Linearförderer ein</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BelongsToUnit</x:t>
@@ -1022,6 +1046,102 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -1034,10 +1154,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
